--- a/Config/Excel/GameConfig/BuffConfig.xlsx
+++ b/Config/Excel/GameConfig/BuffConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,15 +464,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TickInterval</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>MaxStack</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>CanCritical</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ApplyTargetFilter</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
@@ -526,15 +541,30 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -588,15 +618,30 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>持续时间(ms)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>tick间隔(ms)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>最大叠层</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>是否可暴击</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>目标过滤扩展</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
@@ -627,10 +672,19 @@
       <c r="I4" t="n">
         <v>999999</v>
       </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>基础物理伤害</t>
         </is>
@@ -661,10 +715,19 @@
       <c r="I5" t="n">
         <v>999999</v>
       </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>玩家割草版物理伤害</t>
         </is>
@@ -695,10 +758,19 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>500</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>冻结0.5秒</t>
         </is>
@@ -729,10 +801,19 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>冻结1秒</t>
         </is>
@@ -763,10 +844,19 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>冻结1.5秒</t>
         </is>
@@ -797,10 +887,19 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>冻结2秒</t>
         </is>
@@ -831,10 +930,19 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>冻结3秒</t>
         </is>
@@ -865,10 +973,19 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>击退1米</t>
         </is>
@@ -899,10 +1016,19 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>击退2米</t>
         </is>
@@ -933,12 +1059,1010 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>击退3米</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>54001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>基础治疗100HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>54002</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>200</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>中级治疗200HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>54003</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>500</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>强力治疗500HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>55001</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>500</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>500</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>眩晕0.5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>55002</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>眩晕1秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>55003</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>眩晕2秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>56001</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>减速30%-2秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>56002</v>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>减速50%-3秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>56003</v>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>减速70%-2秒-可叠3层</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>57001</v>
+      </c>
+      <c r="C23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>吸血-攻击*1+防御*0.5伤害-回复50%吸血</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>57002</v>
+      </c>
+      <c r="C24" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>吸血-攻击*1.2+防御*0.3伤害-回复30%吸血</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>58001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>200</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>护盾200-持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>58002</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>500</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>护盾500-持续8秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>58003</v>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>护盾1000-持续5秒-可叠3层</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>59001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>增攻50-持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>59002</v>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>100</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>增攻100-持续8秒-可叠3层</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>59003</v>
+      </c>
+      <c r="C30" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>200</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>强力增攻200-持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>510001</v>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>增防30-持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>510002</v>
+      </c>
+      <c r="C32" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>60</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>增防60-持续8秒-可叠3层</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>510003</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>100</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>强力增防100-持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>511001</v>
+      </c>
+      <c r="C34" t="n">
+        <v>11</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>500</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>毒伤-每500ms攻击*0.3伤害-持续3秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>511002</v>
+      </c>
+      <c r="C35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>500</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>猛毒-每500ms攻击*0.5伤害-持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>511003</v>
+      </c>
+      <c r="C36" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>30</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>500</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>剧毒-每500ms攻击*0.4伤害-持续5秒-可叠3层</t>
         </is>
       </c>
     </row>
